--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_valparaiso.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.82508377828018</v>
+      </c>
+      <c r="C2">
         <v>31.18422670108658</v>
-      </c>
-      <c r="C2">
-        <v>26.82508377828018</v>
       </c>
       <c r="D2">
         <v>3.206749391560689</v>
       </c>
       <c r="E2">
-        <v>19.73568937582238</v>
+        <v>16.97690072622845</v>
       </c>
       <c r="F2">
         <v>63.28740989794918</v>
       </c>
       <c r="G2">
-        <v>16.97690072622845</v>
+        <v>19.73568937582238</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.61072902338377</v>
+      </c>
+      <c r="C3">
         <v>26.83356258596974</v>
-      </c>
-      <c r="C3">
-        <v>28.61072902338377</v>
       </c>
       <c r="D3">
         <v>3.726676235390609</v>
       </c>
       <c r="E3">
-        <v>17.26249469064137</v>
+        <v>18.40577658218887</v>
       </c>
       <c r="F3">
         <v>64.33172872716976</v>
       </c>
       <c r="G3">
-        <v>18.40577658218887</v>
+        <v>17.26249469064137</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>27.8236547682472</v>
+      </c>
+      <c r="C4">
         <v>26.31526371870006</v>
-      </c>
-      <c r="C4">
-        <v>27.8236547682472</v>
       </c>
       <c r="D4">
         <v>3.800075920536505</v>
       </c>
       <c r="E4">
-        <v>17.07243308634508</v>
+        <v>18.05102503726426</v>
       </c>
       <c r="F4">
         <v>64.87654187639066</v>
       </c>
       <c r="G4">
-        <v>18.05102503726426</v>
+        <v>17.07243308634508</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>34.5572354211663</v>
+      </c>
+      <c r="C5">
         <v>27.64578833693305</v>
-      </c>
-      <c r="C5">
-        <v>34.5572354211663</v>
       </c>
       <c r="D5">
         <v>3.6171875</v>
       </c>
       <c r="E5">
+        <v>21.30492676431425</v>
+      </c>
+      <c r="F5">
+        <v>61.65113182423436</v>
+      </c>
+      <c r="G5">
         <v>17.0439414114514</v>
-      </c>
-      <c r="F5">
-        <v>61.65113182423435</v>
-      </c>
-      <c r="G5">
-        <v>21.30492676431425</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>33.44664102334735</v>
+      </c>
+      <c r="C6">
         <v>32.95464710618123</v>
-      </c>
-      <c r="C6">
-        <v>33.44664102334735</v>
       </c>
       <c r="D6">
         <v>3.034473398479913</v>
       </c>
       <c r="E6">
-        <v>19.80432211590152</v>
+        <v>20.09998924846791</v>
       </c>
       <c r="F6">
         <v>60.09568863563058</v>
       </c>
       <c r="G6">
-        <v>20.09998924846791</v>
+        <v>19.80432211590152</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>32.18891125741335</v>
+      </c>
+      <c r="C7">
         <v>29.65884977419881</v>
-      </c>
-      <c r="C7">
-        <v>32.18891125741335</v>
       </c>
       <c r="D7">
         <v>3.371674922032655</v>
       </c>
       <c r="E7">
-        <v>18.32515296174276</v>
+        <v>19.88838835473677</v>
       </c>
       <c r="F7">
         <v>61.78645868352048</v>
       </c>
       <c r="G7">
-        <v>19.88838835473677</v>
+        <v>18.32515296174276</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.08445306791954</v>
+      </c>
+      <c r="C8">
         <v>32.57157511213475</v>
-      </c>
-      <c r="C8">
-        <v>26.08445306791954</v>
       </c>
       <c r="D8">
         <v>3.070161625765048</v>
       </c>
       <c r="E8">
+        <v>16.44088369483007</v>
+      </c>
+      <c r="F8">
+        <v>63.02943616268573</v>
+      </c>
+      <c r="G8">
         <v>20.5296801424842</v>
-      </c>
-      <c r="F8">
-        <v>63.02943616268572</v>
-      </c>
-      <c r="G8">
-        <v>16.44088369483007</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>33.87216648086213</v>
+      </c>
+      <c r="C9">
         <v>14.75287997027127</v>
-      </c>
-      <c r="C9">
-        <v>33.87216648086213</v>
       </c>
       <c r="D9">
         <v>6.778337531486146</v>
       </c>
       <c r="E9">
-        <v>9.926240780097512</v>
+        <v>22.7903487935992</v>
       </c>
       <c r="F9">
         <v>67.28341042630329</v>
       </c>
       <c r="G9">
-        <v>22.7903487935992</v>
+        <v>9.926240780097514</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.04905453548918</v>
+      </c>
+      <c r="C10">
         <v>27.97113364392071</v>
-      </c>
-      <c r="C10">
-        <v>29.04905453548918</v>
       </c>
       <c r="D10">
         <v>3.575114304376225</v>
       </c>
       <c r="E10">
-        <v>17.81371807551341</v>
+        <v>18.50020361859329</v>
       </c>
       <c r="F10">
         <v>63.6860783058933</v>
       </c>
       <c r="G10">
-        <v>18.50020361859329</v>
+        <v>17.81371807551341</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>34.93105712409717</v>
+      </c>
+      <c r="C11">
         <v>25.32282775224338</v>
-      </c>
-      <c r="C11">
-        <v>34.93105712409717</v>
       </c>
       <c r="D11">
         <v>3.949006050129646</v>
       </c>
       <c r="E11">
-        <v>15.80169352635892</v>
+        <v>21.79732313575526</v>
       </c>
       <c r="F11">
         <v>62.40098333788583</v>
       </c>
       <c r="G11">
-        <v>21.79732313575526</v>
+        <v>15.80169352635892</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>31.19432071269488</v>
+      </c>
+      <c r="C12">
         <v>24.55456570155902</v>
-      </c>
-      <c r="C12">
-        <v>31.19432071269488</v>
       </c>
       <c r="D12">
         <v>4.072562358276644</v>
       </c>
       <c r="E12">
-        <v>15.76548395745822</v>
+        <v>20.02859951738314</v>
       </c>
       <c r="F12">
         <v>64.20591652515863</v>
       </c>
       <c r="G12">
-        <v>20.02859951738314</v>
+        <v>15.76548395745822</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>30.6964329046348</v>
+      </c>
+      <c r="C13">
         <v>26.97565315861846</v>
-      </c>
-      <c r="C13">
-        <v>30.6964329046348</v>
       </c>
       <c r="D13">
         <v>3.707046476761619</v>
       </c>
       <c r="E13">
-        <v>17.10870568922177</v>
+        <v>19.46852716359719</v>
       </c>
       <c r="F13">
         <v>63.42276714718103</v>
       </c>
       <c r="G13">
-        <v>19.46852716359719</v>
+        <v>17.10870568922177</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>28.05740345592235</v>
+      </c>
+      <c r="C14">
         <v>29.29166143675997</v>
-      </c>
-      <c r="C14">
-        <v>28.05740345592235</v>
       </c>
       <c r="D14">
         <v>3.41394086559063</v>
       </c>
       <c r="E14">
-        <v>18.6157200595618</v>
+        <v>17.83131248670496</v>
       </c>
       <c r="F14">
         <v>63.55296745373325</v>
       </c>
       <c r="G14">
-        <v>17.83131248670496</v>
+        <v>18.6157200595618</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>29.76088201603665</v>
+      </c>
+      <c r="C15">
         <v>27.40549828178694</v>
-      </c>
-      <c r="C15">
-        <v>29.76088201603665</v>
       </c>
       <c r="D15">
         <v>3.648902821316614</v>
       </c>
       <c r="E15">
-        <v>17.43725231175694</v>
+        <v>18.93590853186353</v>
       </c>
       <c r="F15">
         <v>63.62683915637954</v>
       </c>
       <c r="G15">
-        <v>18.93590853186353</v>
+        <v>17.43725231175694</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>26.08462774504553</v>
+      </c>
+      <c r="C16">
         <v>31.33369041242635</v>
-      </c>
-      <c r="C16">
-        <v>26.08462774504553</v>
       </c>
       <c r="D16">
         <v>3.191452991452992</v>
       </c>
       <c r="E16">
+        <v>16.57026199387547</v>
+      </c>
+      <c r="F16">
+        <v>63.52500850629465</v>
+      </c>
+      <c r="G16">
         <v>19.90472949982987</v>
-      </c>
-      <c r="F16">
-        <v>63.52500850629466</v>
-      </c>
-      <c r="G16">
-        <v>16.57026199387547</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>28.61299709020368</v>
+      </c>
+      <c r="C17">
         <v>32.31490462334303</v>
-      </c>
-      <c r="C17">
-        <v>28.61299709020368</v>
       </c>
       <c r="D17">
         <v>3.094547273636818</v>
       </c>
       <c r="E17">
-        <v>20.08036162732295</v>
+        <v>17.78001004520342</v>
       </c>
       <c r="F17">
         <v>62.13962832747362</v>
       </c>
       <c r="G17">
-        <v>17.78001004520342</v>
+        <v>20.08036162732295</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>25.57772071894134</v>
+      </c>
+      <c r="C18">
         <v>32.05609322536046</v>
-      </c>
-      <c r="C18">
-        <v>25.57772071894134</v>
       </c>
       <c r="D18">
         <v>3.119531731361676</v>
       </c>
       <c r="E18">
-        <v>20.33579751910789</v>
+        <v>16.22603683748904</v>
       </c>
       <c r="F18">
         <v>63.43816564340308</v>
       </c>
       <c r="G18">
-        <v>16.22603683748904</v>
+        <v>20.33579751910789</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>28.17830758898589</v>
+      </c>
+      <c r="C19">
         <v>29.11349899261249</v>
-      </c>
-      <c r="C19">
-        <v>28.17830758898589</v>
       </c>
       <c r="D19">
         <v>3.434832756632065</v>
       </c>
       <c r="E19">
-        <v>18.50922792822604</v>
+        <v>17.91466968393411</v>
       </c>
       <c r="F19">
         <v>63.57610238783984</v>
       </c>
       <c r="G19">
-        <v>17.91466968393411</v>
+        <v>18.50922792822604</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>30.55033143209496</v>
+      </c>
+      <c r="C20">
         <v>30.54108216432866</v>
-      </c>
-      <c r="C20">
-        <v>30.55033143209496</v>
       </c>
       <c r="D20">
         <v>3.274278215223097</v>
       </c>
       <c r="E20">
-        <v>18.95885167464115</v>
+        <v>18.96459330143541</v>
       </c>
       <c r="F20">
         <v>62.07655502392344</v>
       </c>
       <c r="G20">
-        <v>18.96459330143541</v>
+        <v>18.95885167464115</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>31.48291591358981</v>
+      </c>
+      <c r="C21">
         <v>26.68043721490661</v>
-      </c>
-      <c r="C21">
-        <v>31.48291591358981</v>
       </c>
       <c r="D21">
         <v>3.748064516129032</v>
       </c>
       <c r="E21">
-        <v>16.86891222724057</v>
+        <v>19.90531642814388</v>
       </c>
       <c r="F21">
         <v>63.22577134461555</v>
       </c>
       <c r="G21">
-        <v>19.90531642814388</v>
+        <v>16.86891222724057</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>29.9701690420948</v>
+      </c>
+      <c r="C22">
         <v>24.95856811402055</v>
-      </c>
-      <c r="C22">
-        <v>29.9701690420948</v>
       </c>
       <c r="D22">
         <v>4.0066401062417</v>
       </c>
       <c r="E22">
-        <v>16.10970861323863</v>
+        <v>19.34448675709212</v>
       </c>
       <c r="F22">
         <v>64.54580462966925</v>
       </c>
       <c r="G22">
-        <v>19.34448675709212</v>
+        <v>16.10970861323863</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>28.11423941664979</v>
+      </c>
+      <c r="C23">
         <v>31.27405306866518</v>
-      </c>
-      <c r="C23">
-        <v>28.11423941664979</v>
       </c>
       <c r="D23">
         <v>3.197538860103627</v>
       </c>
       <c r="E23">
-        <v>19.62129876731478</v>
+        <v>17.63883593849282</v>
       </c>
       <c r="F23">
         <v>62.73986529419241</v>
       </c>
       <c r="G23">
-        <v>17.63883593849282</v>
+        <v>19.62129876731478</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>28.79551446784367</v>
+      </c>
+      <c r="C24">
         <v>28.94569969629209</v>
-      </c>
-      <c r="C24">
-        <v>28.79551446784367</v>
       </c>
       <c r="D24">
         <v>3.45474460970829</v>
       </c>
       <c r="E24">
-        <v>18.35011848341232</v>
+        <v>18.2549085985105</v>
       </c>
       <c r="F24">
         <v>63.39497291807719</v>
       </c>
       <c r="G24">
-        <v>18.2549085985105</v>
+        <v>18.35011848341232</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>28.54712487240558</v>
+      </c>
+      <c r="C25">
         <v>43.08721787456051</v>
-      </c>
-      <c r="C25">
-        <v>28.54712487240558</v>
       </c>
       <c r="D25">
         <v>2.320873914187944</v>
       </c>
       <c r="E25">
-        <v>25.10407718231679</v>
+        <v>16.63252494548338</v>
       </c>
       <c r="F25">
         <v>58.26339787219982</v>
       </c>
       <c r="G25">
-        <v>16.63252494548338</v>
+        <v>25.10407718231679</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>33.06055646481178</v>
+      </c>
+      <c r="C26">
         <v>38.62520458265139</v>
-      </c>
-      <c r="C26">
-        <v>33.06055646481178</v>
       </c>
       <c r="D26">
         <v>2.588983050847458</v>
       </c>
       <c r="E26">
-        <v>22.4976167778837</v>
+        <v>19.25643469971401</v>
       </c>
       <c r="F26">
         <v>58.24594852240228</v>
       </c>
       <c r="G26">
-        <v>19.25643469971401</v>
+        <v>22.4976167778837</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>31.04048759251197</v>
+      </c>
+      <c r="C27">
         <v>45.7553330430997</v>
-      </c>
-      <c r="C27">
-        <v>31.04048759251197</v>
       </c>
       <c r="D27">
         <v>2.185537583254044</v>
       </c>
       <c r="E27">
-        <v>25.88032504309284</v>
+        <v>17.55725190839695</v>
       </c>
       <c r="F27">
         <v>56.56242304851022</v>
       </c>
       <c r="G27">
-        <v>17.55725190839695</v>
+        <v>25.88032504309284</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>30.95656879989176</v>
+      </c>
+      <c r="C28">
         <v>49.74969557570017</v>
-      </c>
-      <c r="C28">
-        <v>30.95656879989176</v>
       </c>
       <c r="D28">
         <v>2.010062550992657</v>
       </c>
       <c r="E28">
-        <v>27.53069781371668</v>
+        <v>17.130877508236</v>
       </c>
       <c r="F28">
         <v>55.33842467804732</v>
       </c>
       <c r="G28">
-        <v>17.130877508236</v>
+        <v>27.53069781371668</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>27.78917671197743</v>
+      </c>
+      <c r="C29">
         <v>29.64862785329572</v>
-      </c>
-      <c r="C29">
-        <v>27.78917671197743</v>
       </c>
       <c r="D29">
         <v>3.372837370242215</v>
       </c>
       <c r="E29">
-        <v>18.83196220575059</v>
+        <v>17.65089191170481</v>
       </c>
       <c r="F29">
         <v>63.51714588254459</v>
       </c>
       <c r="G29">
-        <v>17.65089191170481</v>
+        <v>18.83196220575059</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>30.54412168254342</v>
+      </c>
+      <c r="C30">
         <v>26.19859657375828</v>
-      </c>
-      <c r="C30">
-        <v>30.54412168254342</v>
       </c>
       <c r="D30">
         <v>3.81699835403262</v>
       </c>
       <c r="E30">
-        <v>16.71439468780872</v>
+        <v>19.48678830017382</v>
       </c>
       <c r="F30">
         <v>63.79881701201745</v>
       </c>
       <c r="G30">
-        <v>19.48678830017382</v>
+        <v>16.71439468780872</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>29.63743208781461</v>
+      </c>
+      <c r="C31">
         <v>29.94788779243819</v>
-      </c>
-      <c r="C31">
-        <v>29.63743208781461</v>
       </c>
       <c r="D31">
         <v>3.339133654202147</v>
       </c>
       <c r="E31">
-        <v>18.76606683804627</v>
+        <v>18.57152782602654</v>
       </c>
       <c r="F31">
         <v>62.66240533592719</v>
       </c>
       <c r="G31">
-        <v>18.57152782602654</v>
+        <v>18.76606683804627</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>31.58545634429879</v>
+      </c>
+      <c r="C32">
         <v>28.32673757111056</v>
-      </c>
-      <c r="C32">
-        <v>31.58545634429879</v>
       </c>
       <c r="D32">
         <v>3.530233573455577</v>
       </c>
       <c r="E32">
-        <v>17.71393217586327</v>
+        <v>19.75174973898921</v>
       </c>
       <c r="F32">
         <v>62.53431808514752</v>
       </c>
       <c r="G32">
-        <v>19.75174973898921</v>
+        <v>17.71393217586327</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>25.80150068212824</v>
+      </c>
+      <c r="C33">
         <v>24.01091405184175</v>
-      </c>
-      <c r="C33">
-        <v>25.80150068212824</v>
       </c>
       <c r="D33">
         <v>4.164772727272728</v>
       </c>
       <c r="E33">
-        <v>16.02731929425156</v>
+        <v>17.22253841775754</v>
       </c>
       <c r="F33">
         <v>66.75014228799088</v>
       </c>
       <c r="G33">
-        <v>17.22253841775754</v>
+        <v>16.02731929425156</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>29.13999443362093</v>
+      </c>
+      <c r="C34">
         <v>32.13656183319417</v>
-      </c>
-      <c r="C34">
-        <v>29.13999443362093</v>
       </c>
       <c r="D34">
         <v>3.111720554272517</v>
       </c>
       <c r="E34">
-        <v>19.9263690750115</v>
+        <v>18.06833870225495</v>
       </c>
       <c r="F34">
         <v>62.00529222273354</v>
       </c>
       <c r="G34">
-        <v>18.06833870225495</v>
+        <v>19.9263690750115</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>29.71879215523503</v>
+      </c>
+      <c r="C35">
         <v>27.61232748780741</v>
-      </c>
-      <c r="C35">
-        <v>29.71879215523503</v>
       </c>
       <c r="D35">
         <v>3.621570838030816</v>
       </c>
       <c r="E35">
-        <v>17.55045508508113</v>
+        <v>18.88932858461944</v>
       </c>
       <c r="F35">
-        <v>63.56021633029944</v>
+        <v>63.56021633029943</v>
       </c>
       <c r="G35">
-        <v>18.88932858461944</v>
+        <v>17.55045508508112</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>26.73003764514239</v>
+      </c>
+      <c r="C36">
         <v>31.0944903006645</v>
-      </c>
-      <c r="C36">
-        <v>26.73003764514239</v>
       </c>
       <c r="D36">
         <v>3.216003833253474</v>
       </c>
       <c r="E36">
-        <v>19.70193778202942</v>
+        <v>16.93655478844254</v>
       </c>
       <c r="F36">
         <v>63.36150742952805</v>
       </c>
       <c r="G36">
-        <v>16.93655478844254</v>
+        <v>19.70193778202941</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>29.2643655026668</v>
+      </c>
+      <c r="C37">
         <v>30.50551809734662</v>
-      </c>
-      <c r="C37">
-        <v>29.2643655026668</v>
       </c>
       <c r="D37">
         <v>3.278095447547834</v>
       </c>
       <c r="E37">
-        <v>19.09340947741922</v>
+        <v>18.31657183648617</v>
       </c>
       <c r="F37">
         <v>62.5900186860946</v>
       </c>
       <c r="G37">
-        <v>18.31657183648617</v>
+        <v>19.09340947741922</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>29.6276357110812</v>
+      </c>
+      <c r="C38">
         <v>36.30327501121579</v>
-      </c>
-      <c r="C38">
-        <v>29.6276357110812</v>
       </c>
       <c r="D38">
         <v>2.754572417202175</v>
       </c>
       <c r="E38">
-        <v>21.87854864002595</v>
+        <v>17.85540474774239</v>
       </c>
       <c r="F38">
         <v>60.26604661223165</v>
       </c>
       <c r="G38">
-        <v>17.85540474774239</v>
+        <v>21.87854864002595</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>29.9447889682602</v>
+      </c>
+      <c r="C39">
         <v>28.83141010545046</v>
-      </c>
-      <c r="C39">
-        <v>29.9447889682602</v>
       </c>
       <c r="D39">
         <v>3.468439442755366</v>
       </c>
       <c r="E39">
-        <v>18.1585214116794</v>
+        <v>18.85974670193393</v>
       </c>
       <c r="F39">
         <v>62.98173188638668</v>
       </c>
       <c r="G39">
-        <v>18.85974670193393</v>
+        <v>18.1585214116794</v>
       </c>
     </row>
   </sheetData>
